--- a/User1.xlsx
+++ b/User1.xlsx
@@ -1052,8 +1052,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D571"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:D572"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="0"/>
   <cols>
     <col width="18.9090909090909" customWidth="1" style="1" min="1" max="1"/>
     <col width="9.36363636363636" customWidth="1" style="2" min="2" max="2"/>
@@ -11343,7 +11343,7 @@
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>2022-05-05</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="B515" s="0" t="inlineStr">
@@ -11351,8 +11351,10 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="C515" s="0" t="n">
-        <v>194</v>
+      <c r="C515" s="0" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
       </c>
       <c r="D515" s="0" t="inlineStr">
         <is>
@@ -11363,16 +11365,18 @@
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2021-06-05</t>
         </is>
       </c>
       <c r="B516" s="0" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="C516" s="0" t="n">
-        <v>41</v>
+          <t>水电</t>
+        </is>
+      </c>
+      <c r="C516" s="0" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
       </c>
       <c r="D516" s="0" t="inlineStr">
         <is>
@@ -11383,16 +11387,18 @@
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
+          <t>2021-06-06</t>
         </is>
       </c>
       <c r="B517" s="0" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="C517" s="0" t="n">
-        <v>41</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C517" s="0" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
       </c>
       <c r="D517" s="0" t="inlineStr">
         <is>
@@ -11403,16 +11409,18 @@
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="B518" s="0" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="C518" s="0" t="n">
-        <v>236</v>
+          <t>日常</t>
+        </is>
+      </c>
+      <c r="C518" s="0" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
       </c>
       <c r="D518" s="0" t="inlineStr">
         <is>
@@ -11423,16 +11431,18 @@
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>2022-05-08</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="B519" s="0" t="inlineStr">
         <is>
-          <t>日常</t>
-        </is>
-      </c>
-      <c r="C519" s="0" t="n">
-        <v>292</v>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C519" s="0" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
       </c>
       <c r="D519" s="0" t="inlineStr">
         <is>
@@ -11443,16 +11453,18 @@
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>2022-05-09</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="B520" s="0" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="C520" s="0" t="n">
-        <v>234</v>
+          <t>日常</t>
+        </is>
+      </c>
+      <c r="C520" s="0" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
       </c>
       <c r="D520" s="0" t="inlineStr">
         <is>
@@ -11463,16 +11475,18 @@
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="B521" s="0" t="inlineStr">
         <is>
-          <t>交通</t>
-        </is>
-      </c>
-      <c r="C521" s="0" t="n">
-        <v>120</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C521" s="0" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
       </c>
       <c r="D521" s="0" t="inlineStr">
         <is>
@@ -11483,7 +11497,7 @@
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2021-06-11</t>
         </is>
       </c>
       <c r="B522" s="0" t="inlineStr">
@@ -11491,8 +11505,10 @@
           <t>日常</t>
         </is>
       </c>
-      <c r="C522" s="0" t="n">
-        <v>91</v>
+      <c r="C522" s="0" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
       </c>
       <c r="D522" s="0" t="inlineStr">
         <is>
@@ -11503,16 +11519,18 @@
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>2022-05-11</t>
+          <t>2021-06-12</t>
         </is>
       </c>
       <c r="B523" s="0" t="inlineStr">
         <is>
-          <t>日常</t>
-        </is>
-      </c>
-      <c r="C523" s="0" t="n">
-        <v>91</v>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C523" s="0" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
       </c>
       <c r="D523" s="0" t="inlineStr">
         <is>
@@ -11523,7 +11541,7 @@
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>2022-05-12</t>
+          <t>2021-06-13</t>
         </is>
       </c>
       <c r="B524" s="0" t="inlineStr">
@@ -11531,8 +11549,10 @@
           <t>餐饮</t>
         </is>
       </c>
-      <c r="C524" s="0" t="n">
-        <v>243</v>
+      <c r="C524" s="0" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
       </c>
       <c r="D524" s="0" t="inlineStr">
         <is>
@@ -11543,16 +11563,18 @@
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>2022-05-13</t>
+          <t>2021-06-14</t>
         </is>
       </c>
       <c r="B525" s="0" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C525" s="0" t="n">
-        <v>122</v>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="C525" s="0" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
       </c>
       <c r="D525" s="0" t="inlineStr">
         <is>
@@ -11563,16 +11585,18 @@
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>2022-05-14</t>
+          <t>2021-06-15</t>
         </is>
       </c>
       <c r="B526" s="0" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C526" s="0" t="n">
-        <v>347</v>
+          <t>购物</t>
+        </is>
+      </c>
+      <c r="C526" s="0" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
       </c>
       <c r="D526" s="0" t="inlineStr">
         <is>
@@ -11583,16 +11607,18 @@
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="B527" s="0" t="inlineStr">
         <is>
-          <t>日常</t>
-        </is>
-      </c>
-      <c r="C527" s="0" t="n">
-        <v>471</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C527" s="0" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
       </c>
       <c r="D527" s="0" t="inlineStr">
         <is>
@@ -11603,16 +11629,18 @@
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="B528" s="0" t="inlineStr">
         <is>
-          <t>交通</t>
-        </is>
-      </c>
-      <c r="C528" s="0" t="n">
-        <v>101</v>
+          <t>日常</t>
+        </is>
+      </c>
+      <c r="C528" s="0" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
       </c>
       <c r="D528" s="0" t="inlineStr">
         <is>
@@ -11623,16 +11651,18 @@
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2021-06-18</t>
         </is>
       </c>
       <c r="B529" s="0" t="inlineStr">
         <is>
-          <t>购物</t>
-        </is>
-      </c>
-      <c r="C529" s="0" t="n">
-        <v>68</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C529" s="0" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
       </c>
       <c r="D529" s="0" t="inlineStr">
         <is>
@@ -11643,16 +11673,18 @@
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>2022-05-17</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="B530" s="0" t="inlineStr">
         <is>
-          <t>购物</t>
-        </is>
-      </c>
-      <c r="C530" s="0" t="n">
-        <v>68</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C530" s="0" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
       </c>
       <c r="D530" s="0" t="inlineStr">
         <is>
@@ -11663,16 +11695,18 @@
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>2022-05-18</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="B531" s="0" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="C531" s="0" t="n">
-        <v>116</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C531" s="0" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
       </c>
       <c r="D531" s="0" t="inlineStr">
         <is>
@@ -11683,16 +11717,18 @@
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="B532" s="0" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="C532" s="0" t="n">
-        <v>22</v>
+          <t>水电</t>
+        </is>
+      </c>
+      <c r="C532" s="0" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
       </c>
       <c r="D532" s="0" t="inlineStr">
         <is>
@@ -11703,16 +11739,18 @@
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="B533" s="0" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="C533" s="0" t="n">
-        <v>370</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C533" s="0" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
       </c>
       <c r="D533" s="0" t="inlineStr">
         <is>
@@ -11723,16 +11761,18 @@
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="B534" s="0" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C534" s="0" t="n">
-        <v>294</v>
+          <t>日常</t>
+        </is>
+      </c>
+      <c r="C534" s="0" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
       </c>
       <c r="D534" s="0" t="inlineStr">
         <is>
@@ -11743,16 +11783,18 @@
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2021-06-23</t>
         </is>
       </c>
       <c r="B535" s="0" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C535" s="0" t="n">
-        <v>294</v>
+          <t>日常</t>
+        </is>
+      </c>
+      <c r="C535" s="0" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
       </c>
       <c r="D535" s="0" t="inlineStr">
         <is>
@@ -11763,16 +11805,18 @@
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="B536" s="0" t="inlineStr">
         <is>
-          <t>娱乐</t>
-        </is>
-      </c>
-      <c r="C536" s="0" t="n">
-        <v>481</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C536" s="0" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
       </c>
       <c r="D536" s="0" t="inlineStr">
         <is>
@@ -11783,16 +11827,18 @@
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>2022-05-26</t>
+          <t>2021-06-25</t>
         </is>
       </c>
       <c r="B537" s="0" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C537" s="0" t="n">
-        <v>372</v>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="C537" s="0" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
       </c>
       <c r="D537" s="0" t="inlineStr">
         <is>
@@ -11803,7 +11849,7 @@
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>2022-05-27</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="B538" s="0" t="inlineStr">
@@ -11811,8 +11857,10 @@
           <t>餐饮</t>
         </is>
       </c>
-      <c r="C538" s="0" t="n">
-        <v>336</v>
+      <c r="C538" s="0" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
       </c>
       <c r="D538" s="0" t="inlineStr">
         <is>
@@ -11823,16 +11871,18 @@
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>2022-05-28</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="B539" s="0" t="inlineStr">
         <is>
-          <t>娱乐</t>
-        </is>
-      </c>
-      <c r="C539" s="0" t="n">
-        <v>202</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C539" s="0" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
       </c>
       <c r="D539" s="0" t="inlineStr">
         <is>
@@ -11843,16 +11893,18 @@
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>2022-05-29</t>
+          <t>2021-06-28</t>
         </is>
       </c>
       <c r="B540" s="0" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C540" s="0" t="n">
-        <v>260</v>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="C540" s="0" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
       </c>
       <c r="D540" s="0" t="inlineStr">
         <is>
@@ -11863,16 +11915,18 @@
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="B541" s="0" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C541" s="0" t="n">
-        <v>8</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C541" s="0" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
       <c r="D541" s="0" t="inlineStr">
         <is>
@@ -11883,16 +11937,18 @@
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="B542" s="0" t="inlineStr">
         <is>
-          <t>购物</t>
-        </is>
-      </c>
-      <c r="C542" s="0" t="n">
-        <v>618</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C542" s="0" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
       </c>
       <c r="D542" s="0" t="inlineStr">
         <is>
@@ -11903,16 +11959,18 @@
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="B543" s="0" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="C543" s="0" t="n">
-        <v>117</v>
+          <t>购物</t>
+        </is>
+      </c>
+      <c r="C543" s="0" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
       </c>
       <c r="D543" s="0" t="inlineStr">
         <is>
@@ -11923,16 +11981,18 @@
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>2022-06-03</t>
+          <t>2022-06-02</t>
         </is>
       </c>
       <c r="B544" s="0" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="C544" s="0" t="n">
-        <v>16</v>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="C544" s="0" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
       </c>
       <c r="D544" s="0" t="inlineStr">
         <is>
@@ -11943,16 +12003,18 @@
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>2022-06-04</t>
+          <t>2022-06-03</t>
         </is>
       </c>
       <c r="B545" s="0" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="C545" s="0" t="n">
-        <v>117</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C545" s="0" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="D545" s="0" t="inlineStr">
         <is>
@@ -11963,16 +12025,18 @@
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
+          <t>2022-06-04</t>
         </is>
       </c>
       <c r="B546" s="0" t="inlineStr">
         <is>
-          <t>交通</t>
-        </is>
-      </c>
-      <c r="C546" s="0" t="n">
-        <v>352</v>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="C546" s="0" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
       </c>
       <c r="D546" s="0" t="inlineStr">
         <is>
@@ -11983,16 +12047,18 @@
     <row r="547">
       <c r="A547" s="4" t="inlineStr">
         <is>
-          <t>2022-06-06</t>
+          <t>2022-06-05</t>
         </is>
       </c>
       <c r="B547" s="0" t="inlineStr">
         <is>
-          <t>医疗</t>
-        </is>
-      </c>
-      <c r="C547" s="0" t="n">
-        <v>482</v>
+          <t>交通</t>
+        </is>
+      </c>
+      <c r="C547" s="0" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
       </c>
       <c r="D547" s="0" t="inlineStr">
         <is>
@@ -12003,16 +12069,18 @@
     <row r="548">
       <c r="A548" s="4" t="inlineStr">
         <is>
-          <t>2022-06-07</t>
+          <t>2022-06-06</t>
         </is>
       </c>
       <c r="B548" s="0" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="C548" s="0" t="n">
-        <v>382</v>
+          <t>医疗</t>
+        </is>
+      </c>
+      <c r="C548" s="0" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
       </c>
       <c r="D548" s="0" t="inlineStr">
         <is>
@@ -12023,16 +12091,18 @@
     <row r="549">
       <c r="A549" s="4" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2022-06-07</t>
         </is>
       </c>
       <c r="B549" s="0" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C549" s="0" t="n">
-        <v>216</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C549" s="0" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
       </c>
       <c r="D549" s="0" t="inlineStr">
         <is>
@@ -12048,11 +12118,13 @@
       </c>
       <c r="B550" s="0" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="C550" s="0" t="n">
-        <v>123</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C550" s="0" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
       </c>
       <c r="D550" s="0" t="inlineStr">
         <is>
@@ -12068,11 +12140,13 @@
       </c>
       <c r="B551" s="0" t="inlineStr">
         <is>
-          <t>购物</t>
-        </is>
-      </c>
-      <c r="C551" s="0" t="n">
-        <v>68</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C551" s="0" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
       </c>
       <c r="D551" s="0" t="inlineStr">
         <is>
@@ -12088,11 +12162,13 @@
       </c>
       <c r="B552" s="0" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="C552" s="0" t="n">
-        <v>90</v>
+          <t>购物</t>
+        </is>
+      </c>
+      <c r="C552" s="0" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="D552" s="0" t="inlineStr">
         <is>
@@ -12108,11 +12184,13 @@
       </c>
       <c r="B553" s="0" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="C553" s="0" t="n">
-        <v>72</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C553" s="0" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
       </c>
       <c r="D553" s="0" t="inlineStr">
         <is>
@@ -12128,11 +12206,13 @@
       </c>
       <c r="B554" s="0" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="C554" s="0" t="n">
-        <v>60</v>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="C554" s="0" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
       </c>
       <c r="D554" s="0" t="inlineStr">
         <is>
@@ -12143,16 +12223,18 @@
     <row r="555">
       <c r="A555" s="4" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="B555" s="0" t="inlineStr">
         <is>
-          <t>餐饮</t>
-        </is>
-      </c>
-      <c r="C555" s="0" t="n">
-        <v>111</v>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="C555" s="0" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="D555" s="0" t="inlineStr">
         <is>
@@ -12163,7 +12245,7 @@
     <row r="556">
       <c r="A556" s="4" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="B556" s="0" t="inlineStr">
@@ -12171,8 +12253,10 @@
           <t>餐饮</t>
         </is>
       </c>
-      <c r="C556" s="0" t="n">
-        <v>18</v>
+      <c r="C556" s="0" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
       </c>
       <c r="D556" s="0" t="inlineStr">
         <is>
@@ -12183,7 +12267,7 @@
     <row r="557">
       <c r="A557" s="4" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022-06-10</t>
         </is>
       </c>
       <c r="B557" s="0" t="inlineStr">
@@ -12191,8 +12275,10 @@
           <t>餐饮</t>
         </is>
       </c>
-      <c r="C557" s="0" t="n">
-        <v>106</v>
+      <c r="C557" s="0" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="D557" s="0" t="inlineStr">
         <is>
@@ -12203,16 +12289,18 @@
     <row r="558">
       <c r="A558" s="4" t="inlineStr">
         <is>
-          <t>2022-06-12</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="B558" s="0" t="inlineStr">
         <is>
-          <t>购物</t>
-        </is>
-      </c>
-      <c r="C558" s="0" t="n">
-        <v>88</v>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C558" s="0" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
       </c>
       <c r="D558" s="0" t="inlineStr">
         <is>
@@ -12231,8 +12319,10 @@
           <t>购物</t>
         </is>
       </c>
-      <c r="C559" s="0" t="n">
-        <v>327</v>
+      <c r="C559" s="0" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
       </c>
       <c r="D559" s="0" t="inlineStr">
         <is>
@@ -12243,16 +12333,18 @@
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-06-12</t>
         </is>
       </c>
       <c r="B560" s="0" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="C560" s="0" t="n">
-        <v>121</v>
+          <t>购物</t>
+        </is>
+      </c>
+      <c r="C560" s="0" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
       </c>
       <c r="D560" s="0" t="inlineStr">
         <is>
@@ -12263,16 +12355,18 @@
     <row r="561">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="B561" s="0" t="inlineStr">
         <is>
-          <t>购物</t>
-        </is>
-      </c>
-      <c r="C561" s="0" t="n">
-        <v>41</v>
+          <t>学习</t>
+        </is>
+      </c>
+      <c r="C561" s="0" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
       </c>
       <c r="D561" s="0" t="inlineStr">
         <is>
@@ -12291,8 +12385,10 @@
           <t>购物</t>
         </is>
       </c>
-      <c r="C562" s="0" t="n">
-        <v>158</v>
+      <c r="C562" s="0" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="D562" s="0" t="inlineStr">
         <is>
@@ -12303,16 +12399,18 @@
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
+          <t>2022-06-14</t>
         </is>
       </c>
       <c r="B563" s="0" t="inlineStr">
         <is>
-          <t>日常</t>
-        </is>
-      </c>
-      <c r="C563" s="0" t="n">
-        <v>292</v>
+          <t>购物</t>
+        </is>
+      </c>
+      <c r="C563" s="0" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
       </c>
       <c r="D563" s="0" t="inlineStr">
         <is>
@@ -12323,16 +12421,18 @@
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>2022-06-16</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="B564" s="0" t="inlineStr">
         <is>
-          <t>水电</t>
-        </is>
-      </c>
-      <c r="C564" s="0" t="n">
-        <v>234</v>
+          <t>日常</t>
+        </is>
+      </c>
+      <c r="C564" s="0" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
       </c>
       <c r="D564" s="0" t="inlineStr">
         <is>
@@ -12348,11 +12448,13 @@
       </c>
       <c r="B565" s="0" t="inlineStr">
         <is>
-          <t>学习</t>
-        </is>
-      </c>
-      <c r="C565" s="0" t="n">
-        <v>120</v>
+          <t>水电</t>
+        </is>
+      </c>
+      <c r="C565" s="0" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
       </c>
       <c r="D565" s="0" t="inlineStr">
         <is>
@@ -12368,12 +12470,12 @@
       </c>
       <c r="B566" s="0" t="inlineStr">
         <is>
-          <t>餐饮</t>
+          <t>学习</t>
         </is>
       </c>
       <c r="C566" s="0" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D566" s="0" t="inlineStr">
@@ -12385,17 +12487,17 @@
     <row r="567">
       <c r="A567" s="0" t="inlineStr">
         <is>
-          <t>2022-06-17</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="B567" s="0" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>餐饮</t>
         </is>
       </c>
       <c r="C567" s="0" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D567" s="0" t="inlineStr">
@@ -12412,12 +12514,12 @@
       </c>
       <c r="B568" s="0" t="inlineStr">
         <is>
-          <t>购物</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="C568" s="0" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>435</t>
         </is>
       </c>
       <c r="D568" s="0" t="inlineStr">
@@ -12429,17 +12531,17 @@
     <row r="569">
       <c r="A569" s="0" t="inlineStr">
         <is>
-          <t>2022-06-18</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="B569" s="0" t="inlineStr">
         <is>
-          <t>日常</t>
+          <t>购物</t>
         </is>
       </c>
       <c r="C569" s="0" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D569" s="0" t="inlineStr">
@@ -12456,12 +12558,12 @@
       </c>
       <c r="B570" s="0" t="inlineStr">
         <is>
-          <t>餐饮</t>
+          <t>日常</t>
         </is>
       </c>
       <c r="C570" s="0" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>290</t>
         </is>
       </c>
       <c r="D570" s="0" t="inlineStr">
@@ -12473,18 +12575,42 @@
     <row r="571">
       <c r="A571" s="0" t="inlineStr">
         <is>
+          <t>2022-06-18</t>
+        </is>
+      </c>
+      <c r="B571" s="0" t="inlineStr">
+        <is>
+          <t>餐饮</t>
+        </is>
+      </c>
+      <c r="C571" s="5" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D571" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="0" t="inlineStr">
+        <is>
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="B571" s="0" t="inlineStr">
+      <c r="B572" s="0" t="inlineStr">
         <is>
           <t>学习</t>
         </is>
       </c>
-      <c r="C571" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="D571" s="0" t="inlineStr">
+      <c r="C572" s="0" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D572" s="0" t="inlineStr">
         <is>
           <t>无</t>
         </is>
